--- a/Bug Report/Bug_Tracking_Report.xlsx
+++ b/Bug Report/Bug_Tracking_Report.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FARZAN\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FARZAN\Desktop\API_Testing_RestfulBooker\Bug Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_B9CB6E52D8F5B1029D4E67E6F681C68444A38195" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33212D45-B226-4851-9FDD-C58E141D04ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="30">
   <si>
     <t>Bug ID</t>
   </si>
@@ -82,24 +82,9 @@
     <t>BUG-002</t>
   </si>
   <si>
-    <t>PUT endpoint returns 403 instead of 401 for missing/invalid authentication</t>
-  </si>
-  <si>
-    <t>Update Booking</t>
-  </si>
-  <si>
     <t>Medium</t>
   </si>
   <si>
-    <t>TC_24, TC_25</t>
-  </si>
-  <si>
-    <t>401 Unauthorized</t>
-  </si>
-  <si>
-    <t>403 Forbidden</t>
-  </si>
-  <si>
     <t>BUG-003</t>
   </si>
   <si>
@@ -109,32 +94,29 @@
     <t>Partial Update</t>
   </si>
   <si>
-    <t>TC_030, TC_031</t>
-  </si>
-  <si>
-    <t>401/404 as applicable</t>
-  </si>
-  <si>
-    <t>403/405 returned</t>
-  </si>
-  <si>
-    <t>BUG-004</t>
-  </si>
-  <si>
     <t>DELETE endpoint returns incorrect status codes</t>
   </si>
   <si>
     <t>Delete Booking</t>
   </si>
   <si>
-    <t>TC_034, TC_035</t>
+    <t>TC_031</t>
+  </si>
+  <si>
+    <t>TC_035</t>
+  </si>
+  <si>
+    <t>404 as applicable</t>
+  </si>
+  <si>
+    <t>405 returned</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -147,6 +129,12 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -500,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -576,21 +564,21 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="E3" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>14</v>
@@ -599,30 +587,30 @@
         <v>15</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>14</v>
@@ -631,48 +619,17 @@
         <v>15</v>
       </c>
       <c r="H4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>